--- a/pinktabletracker.xlsx
+++ b/pinktabletracker.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julianestrada/Downloads/interactivetablemap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2529A4-CCDA-6D49-BEBB-68A3747F83C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C1ED0B-F856-D241-8A8E-E9FF0B34753F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33480" yWindow="1280" windowWidth="27240" windowHeight="16440" xr2:uid="{D9F505DB-68D4-8443-8156-E03A2E550FF7}"/>
+    <workbookView xWindow="2280" yWindow="2800" windowWidth="27240" windowHeight="16440" xr2:uid="{D9F505DB-68D4-8443-8156-E03A2E550FF7}"/>
   </bookViews>
   <sheets>
-    <sheet name="coordinates" sheetId="1" r:id="rId1"/>
+    <sheet name="xlsx" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="681">
   <si>
     <t>Coordinates</t>
   </si>
@@ -587,6 +587,12 @@
     <t>x=65.64, y=74.86</t>
   </si>
   <si>
+    <t>D42</t>
+  </si>
+  <si>
+    <t>x=26.03, y=74.78</t>
+  </si>
+  <si>
     <t>D43</t>
   </si>
   <si>
@@ -692,6 +698,12 @@
     <t>x=65.60, y=80.82</t>
   </si>
   <si>
+    <t>D62</t>
+  </si>
+  <si>
+    <t>x=26.03, y=80.96</t>
+  </si>
+  <si>
     <t>D63</t>
   </si>
   <si>
@@ -993,6 +1005,12 @@
   </si>
   <si>
     <t>x=15.64, y=74.78</t>
+  </si>
+  <si>
+    <t>E58</t>
+  </si>
+  <si>
+    <t>x=13.99, y=74.78</t>
   </si>
   <si>
     <t>E59</t>
@@ -5252,39 +5270,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01D9A35-BCCB-8F40-B9B0-5DBBF8FA9648}">
-  <dimension ref="A1:F222"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.5" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="3.33203125" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="26.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B1" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E1" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -5293,15 +5311,15 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -5310,15 +5328,15 @@
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -5327,15 +5345,15 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F4" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -5344,12 +5362,12 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -5358,15 +5376,15 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F6" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B7" t="s">
         <v>36</v>
@@ -5375,15 +5393,15 @@
         <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F7" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -5392,15 +5410,15 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F8" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
@@ -5409,15 +5427,15 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F9" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -5426,15 +5444,15 @@
         <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F10" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B11" t="s">
         <v>54</v>
@@ -5443,15 +5461,15 @@
         <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F11" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B12" t="s">
         <v>58</v>
@@ -5460,15 +5478,15 @@
         <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F12" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -5477,15 +5495,15 @@
         <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F13" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -5494,15 +5512,15 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F14" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B15" t="s">
         <v>46</v>
@@ -5511,15 +5529,15 @@
         <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F15" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -5528,15 +5546,15 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
@@ -5545,15 +5563,15 @@
         <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F17" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -5562,15 +5580,15 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F18" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
@@ -5579,15 +5597,15 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F19" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -5596,15 +5614,15 @@
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F20" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
@@ -5613,15 +5631,15 @@
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F21" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B22" t="s">
         <v>48</v>
@@ -5630,15 +5648,15 @@
         <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F22" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
@@ -5647,15 +5665,15 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F23" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B24" t="s">
         <v>56</v>
@@ -5664,15 +5682,15 @@
         <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F24" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B25" t="s">
         <v>44</v>
@@ -5681,15 +5699,15 @@
         <v>45</v>
       </c>
       <c r="D25" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F25" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -5698,26 +5716,26 @@
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F26" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C27" t="e">
         <v>#N/A</v>
       </c>
       <c r="D27" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B28" t="s">
         <v>50</v>
@@ -5726,15 +5744,15 @@
         <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F28" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B29" t="s">
         <v>52</v>
@@ -5743,15 +5761,15 @@
         <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F29" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B30" t="s">
         <v>117</v>
@@ -5760,15 +5778,15 @@
         <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F30" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B31" t="s">
         <v>108</v>
@@ -5777,15 +5795,15 @@
         <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F31" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B32" t="s">
         <v>72</v>
@@ -5794,15 +5812,15 @@
         <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F32" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B33" t="s">
         <v>127</v>
@@ -5811,15 +5829,15 @@
         <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F33" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B34" t="s">
         <v>62</v>
@@ -5828,15 +5846,15 @@
         <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F34" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B35" t="s">
         <v>70</v>
@@ -5845,15 +5863,15 @@
         <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F35" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B36" t="s">
         <v>66</v>
@@ -5862,15 +5880,15 @@
         <v>67</v>
       </c>
       <c r="D36" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F36" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B37" t="s">
         <v>64</v>
@@ -5879,12 +5897,12 @@
         <v>65</v>
       </c>
       <c r="D37" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B38" t="s">
         <v>60</v>
@@ -5893,15 +5911,15 @@
         <v>61</v>
       </c>
       <c r="D38" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F38" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B39" t="s">
         <v>68</v>
@@ -5910,15 +5928,15 @@
         <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F39" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B40" t="s">
         <v>74</v>
@@ -5927,12 +5945,12 @@
         <v>75</v>
       </c>
       <c r="D40" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B41" t="s">
         <v>121</v>
@@ -5941,12 +5959,12 @@
         <v>122</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B42" t="s">
         <v>129</v>
@@ -5955,12 +5973,12 @@
         <v>130</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B43" t="s">
         <v>110</v>
@@ -5969,12 +5987,12 @@
         <v>111</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s">
         <v>119</v>
@@ -5983,15 +6001,15 @@
         <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E44" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B45" t="s">
         <v>106</v>
@@ -6000,12 +6018,12 @@
         <v>107</v>
       </c>
       <c r="D45" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B46" t="s">
         <v>76</v>
@@ -6014,15 +6032,15 @@
         <v>77</v>
       </c>
       <c r="D46" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F46" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B47" t="s">
         <v>78</v>
@@ -6031,15 +6049,15 @@
         <v>79</v>
       </c>
       <c r="D47" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F47" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B48" t="s">
         <v>80</v>
@@ -6048,15 +6066,15 @@
         <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F48" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B49" t="s">
         <v>84</v>
@@ -6065,15 +6083,15 @@
         <v>85</v>
       </c>
       <c r="D49" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F49" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B50" t="s">
         <v>82</v>
@@ -6082,15 +6100,15 @@
         <v>83</v>
       </c>
       <c r="D50" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F50" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B51" t="s">
         <v>92</v>
@@ -6099,15 +6117,15 @@
         <v>93</v>
       </c>
       <c r="D51" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F51" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B52" t="s">
         <v>88</v>
@@ -6116,15 +6134,15 @@
         <v>89</v>
       </c>
       <c r="D52" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F52" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B53" t="s">
         <v>94</v>
@@ -6133,15 +6151,15 @@
         <v>95</v>
       </c>
       <c r="D53" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F53" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B54" t="s">
         <v>100</v>
@@ -6150,15 +6168,15 @@
         <v>101</v>
       </c>
       <c r="D54" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F54" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B55" t="s">
         <v>98</v>
@@ -6167,18 +6185,18 @@
         <v>99</v>
       </c>
       <c r="D55" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E55" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F55" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B56" t="s">
         <v>102</v>
@@ -6187,15 +6205,15 @@
         <v>103</v>
       </c>
       <c r="D56" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F56" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B57" t="s">
         <v>136</v>
@@ -6204,15 +6222,15 @@
         <v>137</v>
       </c>
       <c r="D57" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F57" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B58" t="s">
         <v>104</v>
@@ -6221,32 +6239,32 @@
         <v>105</v>
       </c>
       <c r="D58" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F58" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B59" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C59" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D59" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F59" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B60" t="s">
         <v>133</v>
@@ -6255,15 +6273,15 @@
         <v>134</v>
       </c>
       <c r="D60" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F60" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B61" t="s">
         <v>138</v>
@@ -6272,15 +6290,15 @@
         <v>139</v>
       </c>
       <c r="D61" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F61" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s">
         <v>86</v>
@@ -6289,15 +6307,15 @@
         <v>87</v>
       </c>
       <c r="D62" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F62" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B63" t="s">
         <v>123</v>
@@ -6306,12 +6324,12 @@
         <v>124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B64" t="s">
         <v>125</v>
@@ -6320,12 +6338,12 @@
         <v>126</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B65" t="s">
         <v>115</v>
@@ -6334,12 +6352,12 @@
         <v>116</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B66" t="s">
         <v>90</v>
@@ -6348,15 +6366,15 @@
         <v>91</v>
       </c>
       <c r="D66" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F66" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B67" t="s">
         <v>96</v>
@@ -6365,12 +6383,12 @@
         <v>97</v>
       </c>
       <c r="D67" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B68" t="s">
         <v>131</v>
@@ -6379,12 +6397,12 @@
         <v>132</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B69" t="s">
         <v>113</v>
@@ -6393,12 +6411,12 @@
         <v>114</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B70" t="s">
         <v>148</v>
@@ -6407,15 +6425,15 @@
         <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F70" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B71" t="s">
         <v>155</v>
@@ -6424,15 +6442,15 @@
         <v>156</v>
       </c>
       <c r="D71" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F71" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B72" t="s">
         <v>164</v>
@@ -6441,32 +6459,32 @@
         <v>165</v>
       </c>
       <c r="D72" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F72" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B73" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C73" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D73" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F73" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B74" t="s">
         <v>162</v>
@@ -6475,15 +6493,15 @@
         <v>163</v>
       </c>
       <c r="D74" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F74" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B75" t="s">
         <v>180</v>
@@ -6492,49 +6510,49 @@
         <v>181</v>
       </c>
       <c r="D75" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F75" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B76" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D76" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F76" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B77" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C77" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D77" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F77" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B78" t="s">
         <v>141</v>
@@ -6543,35 +6561,35 @@
         <v>142</v>
       </c>
       <c r="D78" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F78" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B79" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C79" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D79" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E79" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="F79" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B80" t="s">
         <v>168</v>
@@ -6580,15 +6598,15 @@
         <v>169</v>
       </c>
       <c r="D80" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F80" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B81" t="s">
         <v>159</v>
@@ -6597,15 +6615,15 @@
         <v>160</v>
       </c>
       <c r="D81" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F81" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B82" t="s">
         <v>157</v>
@@ -6614,12 +6632,12 @@
         <v>158</v>
       </c>
       <c r="D82" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B83" t="s">
         <v>145</v>
@@ -6628,15 +6646,15 @@
         <v>146</v>
       </c>
       <c r="D83" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F83" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B84" t="s">
         <v>143</v>
@@ -6645,12 +6663,12 @@
         <v>144</v>
       </c>
       <c r="D84" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B85" t="s">
         <v>150</v>
@@ -6659,12 +6677,12 @@
         <v>151</v>
       </c>
       <c r="D85" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B86" t="s">
         <v>152</v>
@@ -6673,91 +6691,91 @@
         <v>153</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B87" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C87" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D87" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F87" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B88" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C88" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D88" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F88" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C89" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D89" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F89" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C90" t="e">
         <v>#N/A</v>
       </c>
       <c r="D90" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F90" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B91" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C91" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D91" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B92" t="s">
         <v>166</v>
@@ -6766,49 +6784,49 @@
         <v>167</v>
       </c>
       <c r="D92" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F92" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B93" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C93" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D93" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F93" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B94" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C94" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D94" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F94" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B95" t="s">
         <v>170</v>
@@ -6817,134 +6835,134 @@
         <v>171</v>
       </c>
       <c r="D95" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F95" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B96" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C96" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D96" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F96" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B97" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D97" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F97" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B98" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C98" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D98" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F98" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B99" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C99" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D99" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F99" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B100" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C100" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D100" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F100" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B101" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C101" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D101" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F101" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B102" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C102" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D102" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F102" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B103" t="s">
         <v>178</v>
@@ -6953,66 +6971,66 @@
         <v>179</v>
       </c>
       <c r="D103" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F103" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B104" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C104" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D104" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F104" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B105" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C105" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D105" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F105" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B106" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C106" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D106" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F106" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B107" t="s">
         <v>172</v>
@@ -7021,117 +7039,117 @@
         <v>173</v>
       </c>
       <c r="D107" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F107" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B108" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C108" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D108" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F108" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B109" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C109" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D109" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F109" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B110" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C110" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D110" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F110" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B111" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C111" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D111" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F111" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B112" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C112" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D112" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F112" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B113" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C113" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D113" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F113" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B114" t="s">
         <v>175</v>
@@ -7140,1235 +7158,1235 @@
         <v>176</v>
       </c>
       <c r="D114" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F114" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B115" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D115" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B116" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C116" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D116" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E116" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="F116" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B117" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C117" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D117" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E117" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F117" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B118" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C118" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D118" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B119" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C119" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D119" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B120" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C120" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D120" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B121" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C121" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D121" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B122" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C122" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D122" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B123" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C123" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D123" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B124" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C124" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D124" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B125" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C125" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D125" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F125" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B126" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C126" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D126" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F126" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B127" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C127" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D127" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B128" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C128" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D128" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B129" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C129" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D129" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B130" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C130" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="D130" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E130" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="F130" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B131" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C131" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D131" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E131" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="F131" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B132" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C132" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D132" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E132" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="F132" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B133" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C133" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D133" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E133" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="F133" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B134" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C134" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D134" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E134" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="F134" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="B135" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C135" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D135" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E135" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="F135" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="B136" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C136" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D136" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F136" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B137" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C137" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D137" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F137" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B138" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C138" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="D138" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F138" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="B139" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C139" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D139" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E139" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="F139" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="B140" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C140" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D140" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E140" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B141" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C141" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D141" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E141" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B142" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C142" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D142" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B143" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C143" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E143" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="F143" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="B144" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C144" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D144" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F144" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B145" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C145" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D145" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F145" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B146" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C146" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E146" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F146" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B147" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C147" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F147" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B148" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C148" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F148" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B149" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C149" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E149" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="B150" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C150" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D150" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F150" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B151" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C151" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D151" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F151" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B152" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C152" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D152" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F152" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B153" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C153" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D153" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F153" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B154" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C154" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D154" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E154" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="F154" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B155" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C155" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D155" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E155" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="F155" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B156" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C156" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D156" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E156" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="F156" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="B157" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C157" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D157" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B158" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C158" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D158" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F158" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B159" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C159" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D159" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F159" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B160" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C160" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D160" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F160" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B161" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C161" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D161" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F161" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B162" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C162" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D162" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F162" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B163" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C163" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D163" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F163" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B164" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C164" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F164" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B165" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C165" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D165" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F165" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B166" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C166" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D166" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F166" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B167" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C167" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F167" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B168" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C168" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D168" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F168" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B169" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C169" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D169" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F169" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B170" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C170" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D170" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F170" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B171" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C171" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D171" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F171" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B172" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C172" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D172" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E172" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="F172" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B173" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C173" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D173" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F173" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B174" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C174" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D174" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F174" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="B175" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C175" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D175" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F175" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B176" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="C176" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B177" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C177" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D177" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B178" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C178" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D178" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B179" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="C179" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D179" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B180" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C180" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D180" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B181" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C181" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D181" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B182" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C182" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D182" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B183" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C183" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D183" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B184" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C184" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D184" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B185" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C185" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D185" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B186" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C186" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D186" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B187" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C187" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D187" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B188" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C188" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D188" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
@@ -8376,13 +8394,13 @@
         <v>0.5</v>
       </c>
       <c r="B189" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C189" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D189" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
@@ -8390,18 +8408,18 @@
         <v>0.5</v>
       </c>
       <c r="B190" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C190" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D190" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B191" t="s">
         <v>161</v>
@@ -8411,162 +8429,162 @@
         <v>x=68.69, y=66.31</v>
       </c>
       <c r="D191" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B192" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C192" t="str">
         <f>VLOOKUP(B192,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=77.72, y=60.13</v>
       </c>
       <c r="D192" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B193" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C193" t="str">
         <f>VLOOKUP(B193,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=77.72, y=63.29</v>
       </c>
       <c r="D193" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B194" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C194" t="str">
         <f>VLOOKUP(B194,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=77.64, y=66.45</v>
       </c>
       <c r="D194" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B195" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C195" t="str">
         <f>VLOOKUP(B195,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=79.30, y=66.38</v>
       </c>
       <c r="D195" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B196" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C196" t="str">
         <f>VLOOKUP(B196,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=74.52, y=95.26</v>
       </c>
       <c r="D196" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B197" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C197" t="str">
         <f>VLOOKUP(B197,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=74.67, y=92.17</v>
       </c>
       <c r="D197" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B198" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C198" t="str">
         <f>VLOOKUP(B198,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=74.63, y=89.22</v>
       </c>
       <c r="D198" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B199" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C199" t="str">
         <f>VLOOKUP(B199,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=76.21, y=89.22</v>
       </c>
       <c r="D199" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B200" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C200" t="str">
         <f>VLOOKUP(B200,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=76.28, y=86.14</v>
       </c>
       <c r="D200" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="B201" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C201" t="str">
         <f>VLOOKUP(B201,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=80.87, y=85.99</v>
       </c>
       <c r="D201" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B202" t="s">
         <v>135</v>
@@ -8576,15 +8594,15 @@
         <v>x=28.93, y=69.90</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F202" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B203" t="s">
         <v>150</v>
@@ -8594,12 +8612,12 @@
         <v>x=67.18, y=63.22</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B204" t="s">
         <v>143</v>
@@ -8609,57 +8627,57 @@
         <v>x=67.29, y=60.20</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B205" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C205" t="str">
         <f>VLOOKUP(B205,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=12.44, y=60.20</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B206" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C206" t="str">
         <f>VLOOKUP(B206,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=22.83, y=80.89</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B207" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C207" t="str">
         <f>VLOOKUP(B207,[1]Sheet1!A:B,2,FALSE)</f>
         <v>x=24.45, y=80.82</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B208" t="s">
         <v>11</v>
@@ -8669,12 +8687,12 @@
         <v>x=34.47, y=55.39</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B209" t="s">
         <v>112</v>
@@ -8684,138 +8702,138 @@
         <v>x=60.72, y=62.07</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B210" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="C210" t="s">
         <v>140</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B211" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C211" t="s">
         <v>147</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B212" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C212" t="s">
         <v>154</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B213" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C213" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B214" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="C214" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B215" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C215" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B216" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="C216" t="s">
         <v>174</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B217" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C217" t="s">
         <v>177</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B218" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C218" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B219" t="s">
         <v>14</v>
@@ -8824,26 +8842,26 @@
         <v>15</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B220" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C220" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B221" t="s">
         <v>12</v>
@@ -8852,21 +8870,63 @@
         <v>13</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B222" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C222" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>673</v>
+        <v>679</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>666</v>
+      </c>
+      <c r="B223" t="s">
+        <v>182</v>
+      </c>
+      <c r="C223" t="s">
+        <v>183</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>666</v>
+      </c>
+      <c r="B224" t="s">
+        <v>219</v>
+      </c>
+      <c r="C224" t="s">
+        <v>220</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>666</v>
+      </c>
+      <c r="B225" t="s">
+        <v>322</v>
+      </c>
+      <c r="C225" t="s">
+        <v>323</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>668</v>
       </c>
     </row>
   </sheetData>
